--- a/business_surveys/029_data_driven_turf_management_survey--business_surveys.xlsx
+++ b/business_surveys/029_data_driven_turf_management_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Current Solutions Other</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Data Driven Turf Solutions Other</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>data_driven_turf_solutions_title</t>
+          <t>data_driven_turf_solutions_title_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>data_driven_turf_solutions_other</t>
+          <t>data_driven_turf_solutions_other_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Data Driven Turf Solutions Other 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Current Practices Other</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Data Quality Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Standardization Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration Other</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Future Goals Other</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Data Driven Turf Other</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>data_driven_turf_solutions_title_choices</t>
+          <t>data_driven_turf_solutions_title_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>data_driven_turf_solutions_title_choices</t>
+          <t>data_driven_turf_solutions_title_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>data_driven_turf_solutions_title_choices</t>
+          <t>data_driven_turf_solutions_title_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>data_driven_turf_solutions_title_choices</t>
+          <t>data_driven_turf_solutions_title_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
